--- a/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260812.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260812.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>9.88%</t>
+          <t>9.82%</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>176,721,000</t>
+          <t>177,679,000</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>8.98%</t>
+          <t>9.28%</t>
         </is>
       </c>
     </row>
@@ -655,7 +655,7 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>368,639,486</t>
+          <t>369,839,486</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -677,12 +677,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>38,827,000</t>
+          <t>39,027,000</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>5.25%</t>
+          <t>5.34%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>3.85%</t>
+          <t>3.77%</t>
         </is>
       </c>
     </row>
@@ -721,12 +721,12 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>186,546,000</t>
+          <t>187,696,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.70%</t>
+          <t>3.71%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.40%</t>
+          <t>3.36%</t>
         </is>
       </c>
     </row>
@@ -787,12 +787,12 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>5,037,000</t>
+          <t>5,068,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.26%</t>
+          <t>3.27%</t>
         </is>
       </c>
     </row>
@@ -809,12 +809,12 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>454,725,000</t>
+          <t>460,625,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.20%</t>
+          <t>3.19%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.99%</t>
+          <t>3.00%</t>
         </is>
       </c>
     </row>
@@ -853,78 +853,78 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>364,639,964</t>
+          <t>366,839,964</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.90%</t>
+          <t>2.87%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>63,040,000</t>
+          <t>31,356,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.73%</t>
+          <t>2.70%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>131,819,945</t>
+          <t>64,640,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.72%</t>
+          <t>2.69%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>31,356,000</t>
+          <t>132,169,945</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.72%</t>
+          <t>2.69%</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>26,144,000</t>
+          <t>26,288,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.65%</t>
+          <t>2.62%</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>82,730,000</t>
+          <t>83,240,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.55%</t>
+          <t>2.59%</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>97,953,442</t>
+          <t>98,557,442</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2.49%</t>
+          <t>2.52%</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2.37%</t>
+          <t>2.36%</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2.33%</t>
+          <t>2.32%</t>
         </is>
       </c>
     </row>
@@ -1095,12 +1095,12 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>28,764,000</t>
+          <t>28,941,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2.27%</t>
+          <t>2.19%</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>2.18%</t>
+          <t>2.17%</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>2.02%</t>
+          <t>2.15%</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>188,180,000</t>
+          <t>189,341,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.97%</t>
+          <t>2.10%</t>
         </is>
       </c>
     </row>
@@ -1188,24 +1188,24 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.95%</t>
+          <t>1.94%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>鈊  象</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>14,253,000</t>
+          <t>273,066,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1217,22 +1217,22 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>鈊  象</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>273,066,000</t>
+          <t>14,253,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.84%</t>
+          <t>1.79%</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.81%</t>
+          <t>1.79%</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>1.72%</t>
+          <t>1.69%</t>
         </is>
       </c>
     </row>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>13,969,775,538</t>
+          <t>12,645,231,321</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr"/>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>4,679,445,183</t>
+          <t>4,856,672,383</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr"/>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>-45,859,339</t>
+          <t>-76,883,145</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr"/>
